--- a/artfynd/A 4385-2023 artfynd.xlsx
+++ b/artfynd/A 4385-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118308464</v>
+        <v>118308592</v>
       </c>
       <c r="B2" t="n">
         <v>97824</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>704430</v>
+        <v>704316</v>
       </c>
       <c r="R2" t="n">
-        <v>6647849</v>
+        <v>6647874</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118308592</v>
+        <v>118308464</v>
       </c>
       <c r="B3" t="n">
         <v>97824</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>704316</v>
+        <v>704430</v>
       </c>
       <c r="R3" t="n">
-        <v>6647874</v>
+        <v>6647849</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 4385-2023 artfynd.xlsx
+++ b/artfynd/A 4385-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118308592</v>
+        <v>118308464</v>
       </c>
       <c r="B2" t="n">
         <v>97824</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>704316</v>
+        <v>704430</v>
       </c>
       <c r="R2" t="n">
-        <v>6647874</v>
+        <v>6647849</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118308464</v>
+        <v>118308592</v>
       </c>
       <c r="B3" t="n">
         <v>97824</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>704430</v>
+        <v>704316</v>
       </c>
       <c r="R3" t="n">
-        <v>6647849</v>
+        <v>6647874</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 4385-2023 artfynd.xlsx
+++ b/artfynd/A 4385-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118308464</v>
+        <v>118308592</v>
       </c>
       <c r="B2" t="n">
-        <v>97824</v>
+        <v>97831</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>704430</v>
+        <v>704316</v>
       </c>
       <c r="R2" t="n">
-        <v>6647849</v>
+        <v>6647874</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118308592</v>
+        <v>118308464</v>
       </c>
       <c r="B3" t="n">
-        <v>97824</v>
+        <v>97831</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>704316</v>
+        <v>704430</v>
       </c>
       <c r="R3" t="n">
-        <v>6647874</v>
+        <v>6647849</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 4385-2023 artfynd.xlsx
+++ b/artfynd/A 4385-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118308592</v>
+        <v>118308464</v>
       </c>
       <c r="B2" t="n">
-        <v>97831</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Edsbackarna (Edsbackarna), Upl</t>
+          <t>Edsbackarna, Edsbackarna, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>704316</v>
+        <v>704430</v>
       </c>
       <c r="R2" t="n">
-        <v>6647874</v>
+        <v>6647849</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118308464</v>
+        <v>118308592</v>
       </c>
       <c r="B3" t="n">
-        <v>97831</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Edsbackarna (Edsbackarna), Upl</t>
+          <t>Edsbackarna, Edsbackarna, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>704430</v>
+        <v>704316</v>
       </c>
       <c r="R3" t="n">
-        <v>6647849</v>
+        <v>6647874</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 4385-2023 artfynd.xlsx
+++ b/artfynd/A 4385-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308464</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,8 +896,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308592</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>